--- a/excel_routes/route_AHB_CCE_threats.xlsx
+++ b/excel_routes/route_AHB_CCE_threats.xlsx
@@ -54,14 +54,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>06-APR-26</t>
+          <t>20-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,26 +551,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-512</t>
+          <t>Nile Air NP-144</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1140</v>
+        <v>1101</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1199</v>
+        <v>1368</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-59</v>
+        <v>-267</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>06-APR-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,17 +596,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-512</t>
+          <t>flyadeal F3-346</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1140</v>
+        <v>1495</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1199</v>
+        <v>1947</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-59</v>
+        <v>-452</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -617,9 +617,9 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09-APR-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-512</t>
+          <t>flyadeal F3-436</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>802</v>
+        <v>1895</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>826</v>
+        <v>1947</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-24</v>
+        <v>-52</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09-APR-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,17 +686,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-512</t>
+          <t>flyadeal F3-338</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>802</v>
+        <v>1935</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>826</v>
+        <v>1947</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-24</v>
+        <v>-12</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>11-APR-26</t>
+          <t>30-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-514</t>
+          <t>Nile Air NP-144</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>677</v>
+        <v>763</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>826</v>
+        <v>783</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-149</v>
+        <v>-20</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>11-APR-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,26 +776,26 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-514</t>
+          <t>Air Arabia Egypt E5-512</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>677</v>
+        <v>929</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>826</v>
+        <v>848</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-149</v>
+        <v>81</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>13-APR-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-512</t>
+          <t>Nile Air NP-144</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>671</v>
+        <v>648</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>761</v>
+        <v>710</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-90</v>
+        <v>-62</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>13-APR-26</t>
+          <t>11-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>671</v>
+        <v>912</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>761</v>
+        <v>783</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-90</v>
+        <v>129</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>16-MAY-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,30 +911,30 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-514</t>
+          <t>Nile Air NP-144</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1017</v>
+        <v>1271</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1541</v>
+        <v>1368</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-524</v>
+        <v>-97</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>16-MAY-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,30 +956,30 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-514</t>
+          <t>flyadeal F3-346</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1017</v>
+        <v>1545</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1541</v>
+        <v>1563</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-524</v>
+        <v>-18</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>18-MAY-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,30 +1001,30 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-512</t>
+          <t>Nile Air NP-144</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1012</v>
+        <v>1471</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1541</v>
+        <v>1563</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-529</v>
+        <v>-92</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>18-MAY-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,30 +1046,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-512</t>
+          <t>Nile Air NP-144</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1012</v>
+        <v>1271</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1541</v>
+        <v>1368</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-529</v>
+        <v>-97</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20-MAY-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,26 +1091,26 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-144</t>
+          <t>flyadeal F3-14</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1271</v>
+        <v>1068</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1541</v>
+        <v>1368</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-270</v>
+        <v>-300</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>20-MAY-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,26 +1136,26 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-144</t>
+          <t>flyadeal F3-20</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1271</v>
+        <v>1118</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1541</v>
+        <v>1368</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-270</v>
+        <v>-250</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,26 +1181,26 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-512</t>
+          <t>flyadeal F3-22</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1345</v>
+        <v>1118</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1541</v>
+        <v>1368</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-196</v>
+        <v>-250</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,26 +1226,26 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-512</t>
+          <t>flyadeal F3-28</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1345</v>
+        <v>1118</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1541</v>
+        <v>1368</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-196</v>
+        <v>-250</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,26 +1271,26 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-514</t>
+          <t>flyadeal F3-14</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1350</v>
+        <v>1018</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1541</v>
+        <v>1368</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-191</v>
+        <v>-350</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,26 +1316,26 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-514</t>
+          <t>Air Arabia Egypt E5-512</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1350</v>
+        <v>1063</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1541</v>
+        <v>1368</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-191</v>
+        <v>-305</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,26 +1361,26 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-512</t>
+          <t>flyadeal F3-28</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1345</v>
+        <v>1068</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1541</v>
+        <v>1368</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-196</v>
+        <v>-300</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,17 +1406,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-512</t>
+          <t>flyadeal F3-20</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1345</v>
+        <v>1185</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1541</v>
+        <v>1368</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-196</v>
+        <v>-183</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>30</v>
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-512</t>
+          <t>flyadeal F3-22</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>727</v>
+        <v>1185</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>826</v>
+        <v>1368</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-99</v>
+        <v>-183</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>30</v>
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,26 +1496,26 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-512</t>
+          <t>flyadeal F3-22</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>727</v>
+        <v>1008</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>826</v>
+        <v>1368</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-99</v>
+        <v>-360</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,26 +1541,26 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-144</t>
+          <t>flyadeal F3-28</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>640</v>
+        <v>1018</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>826</v>
+        <v>1368</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-186</v>
+        <v>-350</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,26 +1586,26 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-144</t>
+          <t>flyadeal F3-438</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>640</v>
+        <v>1088</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>826</v>
+        <v>1368</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-186</v>
+        <v>-280</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-512</t>
+          <t>flyadeal F3-14</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>727</v>
+        <v>1195</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>826</v>
+        <v>1368</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-99</v>
+        <v>-173</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>30</v>
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-512</t>
+          <t>Nile Air NP-144</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>727</v>
+        <v>1271</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>826</v>
+        <v>1368</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-99</v>
+        <v>-97</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>30</v>
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,14 +1721,14 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-514</t>
+          <t>flyadeal F3-20</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>733</v>
+        <v>1275</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>826</v>
+        <v>1368</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>-93</v>
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,26 +1766,26 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-514</t>
+          <t>flyadeal F3-14</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>733</v>
+        <v>958</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>826</v>
+        <v>1368</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-93</v>
+        <v>-410</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,26 +1811,26 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-512</t>
+          <t>flyadeal F3-22</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>727</v>
+        <v>1058</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>826</v>
+        <v>1368</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-99</v>
+        <v>-310</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1860,22 +1860,22 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>727</v>
+        <v>1063</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>826</v>
+        <v>1368</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-99</v>
+        <v>-305</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,26 +1901,26 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-144</t>
+          <t>flyadeal F3-20</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>640</v>
+        <v>1118</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>826</v>
+        <v>1368</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-186</v>
+        <v>-250</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,26 +1946,26 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-144</t>
+          <t>flyadeal F3-438</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>640</v>
+        <v>1138</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>826</v>
+        <v>1368</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-186</v>
+        <v>-230</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-512</t>
+          <t>flyadeal F3-28</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>1345</v>
+        <v>1195</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>1768</v>
+        <v>1368</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-423</v>
+        <v>-173</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>30</v>
@@ -2012,9 +2012,9 @@
       <c r="I34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,17 +2036,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-512</t>
+          <t>flyadeal F3-346</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>1345</v>
+        <v>905</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>1768</v>
+        <v>1368</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-423</v>
+        <v>-463</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>30</v>
@@ -2057,7 +2057,7 @@
       <c r="I35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J35" s="5" t="inlineStr">
+      <c r="J35" s="4" t="inlineStr">
         <is>
           <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2085,26 +2085,26 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>1350</v>
+        <v>1069</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>1768</v>
+        <v>1368</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-418</v>
+        <v>-299</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>10</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-514</t>
+          <t>flyadeal F3-14</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>1350</v>
+        <v>1115</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>1768</v>
+        <v>1368</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-418</v>
+        <v>-253</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>30</v>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,17 +2171,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-512</t>
+          <t>flyadeal F3-20</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>1345</v>
+        <v>1155</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1768</v>
+        <v>1368</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-423</v>
+        <v>-213</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>30</v>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-512</t>
+          <t>flyadeal F3-22</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>1345</v>
+        <v>1155</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>1768</v>
+        <v>1368</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-423</v>
+        <v>-213</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>30</v>
@@ -2239,10 +2239,910 @@
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>18-JUL-26</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SM-444</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-28</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>1155</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>1368</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>-213</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>18-JUL-26</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>SM-444</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-438</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>1315</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>1368</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>-53</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>22-JUL-26</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>SM-444</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-342</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>758</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>1368</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>-610</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>22-JUL-26</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>SM-444</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-338</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>758</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>1368</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>-610</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>22-JUL-26</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>SM-444</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-346</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>1368</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>-600</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>22-JUL-26</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>SM-444</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-20</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>878</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>1368</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>-490</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>22-JUL-26</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>SM-444</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-22</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>878</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>1368</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>-490</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>22-JUL-26</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>SM-444</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-14</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>938</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>1368</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>-430</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>22-JUL-26</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>SM-444</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-28</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>938</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>1368</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>-430</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>22-JUL-26</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>SM-444</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-438</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>988</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>1368</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>-380</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>22-JUL-26</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>SM-444</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-144</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>1101</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>1368</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>-267</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>23-JUL-26</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>SM-444</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-346</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>758</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>1368</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>-610</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>23-JUL-26</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>SM-444</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-512</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>776</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>1368</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>-592</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
           <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>23-JUL-26</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>SM-444</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-338</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>788</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>1368</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>-580</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>23-JUL-26</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>SM-444</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-14</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>1368</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>-450</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>23-JUL-26</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>SM-444</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-22</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>958</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>1368</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>-410</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>23-JUL-26</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>SM-444</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-342</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>965</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>1368</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>-403</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>23-JUL-26</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>SM-444</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-28</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>978</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>1368</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>-390</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>23-JUL-26</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>SM-444</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-20</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>1195</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>1368</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>-173</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>23-JUL-26</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>SM-444</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-438</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>1215</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>1368</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>-153</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_AHB_CCE_threats.xlsx
+++ b/excel_routes/route_AHB_CCE_threats.xlsx
@@ -54,14 +54,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K59"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,12 +541,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>20-MAY-26</t>
+          <t>24-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SM-444</t>
+          <t>SM-968</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -558,19 +558,19 @@
         <v>1101</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1368</v>
+        <v>1143</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-267</v>
+        <v>-42</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>30-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,17 +596,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-346</t>
+          <t>Nile Air NP-144</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1495</v>
+        <v>648</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1947</v>
+        <v>710</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-452</v>
+        <v>-62</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -617,9 +617,9 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-436</t>
+          <t>Nile Air NP-144</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1895</v>
+        <v>571</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1947</v>
+        <v>626</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-52</v>
+        <v>-55</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,17 +686,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-338</t>
+          <t>Nile Air NP-144</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1935</v>
+        <v>571</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1947</v>
+        <v>626</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-12</v>
+        <v>-55</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>763</v>
+        <v>671</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>783</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-20</v>
+        <v>-112</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,26 +776,26 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-512</t>
+          <t>flyadeal F3-346</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>929</v>
+        <v>948</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>848</v>
+        <v>1221</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>81</v>
+        <v>-273</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>648</v>
+        <v>1271</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>710</v>
+        <v>1368</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-62</v>
+        <v>-97</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,26 +866,26 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-512</t>
+          <t>flyadeal F3-342</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>912</v>
+        <v>1138</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>783</v>
+        <v>1368</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>129</v>
+        <v>-230</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -918,10 +918,10 @@
         <v>1271</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1368</v>
+        <v>1563</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-97</v>
+        <v>-292</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -932,9 +932,9 @@
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-346</t>
+          <t>Nile Air NP-144</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1545</v>
+        <v>1271</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1563</v>
+        <v>1368</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-18</v>
+        <v>-97</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,26 +1001,26 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-144</t>
+          <t>flyadeal F3-20</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1471</v>
+        <v>1118</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1563</v>
+        <v>1368</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-92</v>
+        <v>-250</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,26 +1046,26 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-144</t>
+          <t>flyadeal F3-22</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1271</v>
+        <v>1118</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-97</v>
+        <v>-250</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-14</t>
+          <t>flyadeal F3-438</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1068</v>
+        <v>988</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-300</v>
+        <v>-380</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>15</v>
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-20</t>
+          <t>flyadeal F3-22</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1118</v>
+        <v>1008</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-250</v>
+        <v>-360</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>15</v>
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-22</t>
+          <t>flyadeal F3-14</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1118</v>
+        <v>1018</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-250</v>
+        <v>-350</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>15</v>
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-28</t>
+          <t>flyadeal F3-20</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1118</v>
+        <v>1068</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-250</v>
+        <v>-300</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>15</v>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-14</t>
+          <t>flyadeal F3-28</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1018</v>
+        <v>1068</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-350</v>
+        <v>-300</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>15</v>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,26 +1316,26 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-512</t>
+          <t>Nile Air NP-144</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1063</v>
+        <v>1271</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-305</v>
+        <v>-97</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-28</t>
+          <t>flyadeal F3-346</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1068</v>
+        <v>728</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-300</v>
+        <v>-640</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>15</v>
@@ -1382,9 +1382,9 @@
       <c r="I20" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,30 +1406,30 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-20</t>
+          <t>flyadeal F3-14</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1185</v>
+        <v>878</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-183</v>
+        <v>-490</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>15</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,26 +1451,26 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-22</t>
+          <t>flyadeal F3-28</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>1185</v>
+        <v>978</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-183</v>
+        <v>-390</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-22</t>
+          <t>flyadeal F3-20</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>1008</v>
+        <v>1018</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-360</v>
+        <v>-350</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>15</v>
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-28</t>
+          <t>flyadeal F3-22</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,26 +1586,26 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-438</t>
+          <t>Air Arabia Egypt E5-514</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>1088</v>
+        <v>1058</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-280</v>
+        <v>-310</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,26 +1631,26 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-14</t>
+          <t>flyadeal F3-438</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1195</v>
+        <v>1088</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-173</v>
+        <v>-280</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,30 +1676,30 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-144</t>
+          <t>flyadeal F3-346</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1271</v>
+        <v>698</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-97</v>
+        <v>-670</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>15</v>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,30 +1721,30 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-20</t>
+          <t>flyadeal F3-342</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>1275</v>
+        <v>758</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-93</v>
+        <v>-610</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>15</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,17 +1766,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-14</t>
+          <t>flyadeal F3-338</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>958</v>
+        <v>758</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-410</v>
+        <v>-610</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>15</v>
@@ -1787,9 +1787,9 @@
       <c r="I29" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,30 +1811,30 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-22</t>
+          <t>Air Arabia Egypt E5-512</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>1058</v>
+        <v>768</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-310</v>
+        <v>-600</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>10</v>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,30 +1856,30 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-512</t>
+          <t>flyadeal F3-20</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1063</v>
+        <v>878</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-305</v>
+        <v>-490</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>15</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,17 +1901,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-20</t>
+          <t>flyadeal F3-22</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1118</v>
+        <v>878</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-250</v>
+        <v>-490</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>15</v>
@@ -1922,9 +1922,9 @@
       <c r="I32" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1950,13 +1950,13 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>1138</v>
+        <v>938</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-230</v>
+        <v>-430</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>15</v>
@@ -1967,9 +1967,9 @@
       <c r="I33" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,30 +1991,30 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-28</t>
+          <t>flyadeal F3-14</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>1195</v>
+        <v>938</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-173</v>
+        <v>-430</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>15</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,30 +2036,30 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-346</t>
+          <t>flyadeal F3-28</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>905</v>
+        <v>938</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-463</v>
+        <v>-430</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,30 +2081,30 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-514</t>
+          <t>Nile Air NP-144</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>1069</v>
+        <v>671</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-299</v>
+        <v>-697</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>0</v>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,28 +2126,28 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-14</t>
+          <t>flyadeal F3-342</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>1115</v>
+        <v>758</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-253</v>
+        <v>-610</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="5" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
         <is>
           <t>MEDIUM THREAT - MONITOR</t>
         </is>
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,28 +2171,28 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-20</t>
+          <t>flyadeal F3-338</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>1155</v>
+        <v>758</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-213</v>
+        <v>-610</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="5" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
         <is>
           <t>MEDIUM THREAT - MONITOR</t>
         </is>
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,28 +2216,28 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-22</t>
+          <t>flyadeal F3-346</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>1155</v>
+        <v>768</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-213</v>
+        <v>-600</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="5" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
         <is>
           <t>MEDIUM THREAT - MONITOR</t>
         </is>
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,28 +2261,28 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-28</t>
+          <t>flyadeal F3-20</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>1155</v>
+        <v>878</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-213</v>
+        <v>-490</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="5" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
         <is>
           <t>MEDIUM THREAT - MONITOR</t>
         </is>
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,30 +2306,30 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-438</t>
+          <t>flyadeal F3-22</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1315</v>
+        <v>878</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-53</v>
+        <v>-490</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>15</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-342</t>
+          <t>flyadeal F3-438</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>758</v>
+        <v>938</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-610</v>
+        <v>-430</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>15</v>
@@ -2372,7 +2372,7 @@
       <c r="I42" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J42" s="5" t="inlineStr">
+      <c r="J42" s="4" t="inlineStr">
         <is>
           <t>MEDIUM THREAT - MONITOR</t>
         </is>
@@ -2396,17 +2396,17 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-338</t>
+          <t>flyadeal F3-14</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>758</v>
+        <v>938</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-610</v>
+        <v>-430</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>15</v>
@@ -2417,7 +2417,7 @@
       <c r="I43" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J43" s="5" t="inlineStr">
+      <c r="J43" s="4" t="inlineStr">
         <is>
           <t>MEDIUM THREAT - MONITOR</t>
         </is>
@@ -2441,17 +2441,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-346</t>
+          <t>flyadeal F3-28</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>768</v>
+        <v>938</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-600</v>
+        <v>-430</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>15</v>
@@ -2462,7 +2462,7 @@
       <c r="I44" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J44" s="5" t="inlineStr">
+      <c r="J44" s="4" t="inlineStr">
         <is>
           <t>MEDIUM THREAT - MONITOR</t>
         </is>
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-20</t>
+          <t>flyadeal F3-346</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>878</v>
+        <v>698</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-490</v>
+        <v>-670</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>15</v>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2531,17 +2531,17 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-22</t>
+          <t>flyadeal F3-342</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>878</v>
+        <v>758</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-490</v>
+        <v>-610</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>15</v>
@@ -2552,7 +2552,7 @@
       <c r="I46" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J46" s="5" t="inlineStr">
+      <c r="J46" s="4" t="inlineStr">
         <is>
           <t>MEDIUM THREAT - MONITOR</t>
         </is>
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,30 +2576,30 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-14</t>
+          <t>Air Arabia Egypt E5-514</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>938</v>
+        <v>774</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-430</v>
+        <v>-594</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-28</t>
+          <t>flyadeal F3-22</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>938</v>
+        <v>908</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-430</v>
+        <v>-460</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>15</v>
@@ -2642,7 +2642,7 @@
       <c r="I48" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J48" s="5" t="inlineStr">
+      <c r="J48" s="4" t="inlineStr">
         <is>
           <t>MEDIUM THREAT - MONITOR</t>
         </is>
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-438</t>
+          <t>flyadeal F3-14</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>988</v>
+        <v>908</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-380</v>
+        <v>-460</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>15</v>
@@ -2687,9 +2687,9 @@
       <c r="I49" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2711,17 +2711,17 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-144</t>
+          <t>flyadeal F3-338</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>1101</v>
+        <v>935</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-267</v>
+        <v>-433</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>30</v>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2756,17 +2756,17 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-346</t>
+          <t>flyadeal F3-438</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>758</v>
+        <v>938</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-610</v>
+        <v>-430</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>15</v>
@@ -2777,7 +2777,7 @@
       <c r="I51" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J51" s="5" t="inlineStr">
+      <c r="J51" s="4" t="inlineStr">
         <is>
           <t>MEDIUM THREAT - MONITOR</t>
         </is>
@@ -2791,7 +2791,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2801,30 +2801,30 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-512</t>
+          <t>flyadeal F3-28</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>776</v>
+        <v>938</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-592</v>
+        <v>-430</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -2836,7 +2836,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-338</t>
+          <t>flyadeal F3-20</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>788</v>
+        <v>968</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>1368</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-580</v>
+        <v>-400</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>15</v>
@@ -2867,282 +2867,12 @@
       <c r="I53" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J53" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>23-JUL-26</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>SM-444</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-14</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="E54" s="2" t="n">
-        <v>1368</v>
-      </c>
-      <c r="F54" s="2" t="n">
-        <v>-450</v>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I54" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J54" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>23-JUL-26</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>SM-444</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-22</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="n">
-        <v>958</v>
-      </c>
-      <c r="E55" s="2" t="n">
-        <v>1368</v>
-      </c>
-      <c r="F55" s="2" t="n">
-        <v>-410</v>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I55" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>23-JUL-26</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>SM-444</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-342</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="n">
-        <v>965</v>
-      </c>
-      <c r="E56" s="2" t="n">
-        <v>1368</v>
-      </c>
-      <c r="F56" s="2" t="n">
-        <v>-403</v>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>23-JUL-26</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>SM-444</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-28</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="n">
-        <v>978</v>
-      </c>
-      <c r="E57" s="2" t="n">
-        <v>1368</v>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>-390</v>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I57" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>23-JUL-26</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>SM-444</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-20</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="n">
-        <v>1195</v>
-      </c>
-      <c r="E58" s="2" t="n">
-        <v>1368</v>
-      </c>
-      <c r="F58" s="2" t="n">
-        <v>-173</v>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H58" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>23-JUL-26</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>SM-444</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-438</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="n">
-        <v>1215</v>
-      </c>
-      <c r="E59" s="2" t="n">
-        <v>1368</v>
-      </c>
-      <c r="F59" s="2" t="n">
-        <v>-153</v>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H59" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
